--- a/doc2/TB_LMS_FORUM-TB_LMS_DSCS.xlsx
+++ b/doc2/TB_LMS_FORUM-TB_LMS_DSCS.xlsx
@@ -9,17 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7920"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7920" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TB_LMS_FORUM-TB_LMS_DSCS 매핑 업데이" sheetId="1" r:id="rId1"/>
+    <sheet name="토론평가" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="184">
   <si>
     <t>asis_column (기존)</t>
   </si>
@@ -634,11 +635,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>루브릭점수' 토론에서는 제외됨.
-'시험대체' 등에서는 사용됨.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>1.</t>
     </r>
@@ -1642,6 +1638,391 @@
   </si>
   <si>
     <t>PROS_CONS_FORUM_CFG</t>
+  </si>
+  <si>
+    <t>Query ID</t>
+  </si>
+  <si>
+    <t>유형</t>
+  </si>
+  <si>
+    <t>설명</t>
+  </si>
+  <si>
+    <t>selectForumScoreStatus</t>
+  </si>
+  <si>
+    <t>Select</t>
+  </si>
+  <si>
+    <t>토론 현황(미참여, 완료, 평균/최고/최저 점수) 통계 조회</t>
+  </si>
+  <si>
+    <t>listPaging</t>
+  </si>
+  <si>
+    <t>토론 참여 학습자 목록 조회 (페이징, 팀 정보, 참여 건수 포함)</t>
+  </si>
+  <si>
+    <t>insertStdScore</t>
+  </si>
+  <si>
+    <t>Insert</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">학습자 점수 반영 (Oracle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>MERGE INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 사용)</t>
+    </r>
+  </si>
+  <si>
+    <t>listStdScore</t>
+  </si>
+  <si>
+    <t>학습자별 참여 여부 및 팀 정보 목록 조회</t>
+  </si>
+  <si>
+    <t>selectForumJoinUser</t>
+  </si>
+  <si>
+    <t>특정 학습자의 토론 참여 상세 정보 조회</t>
+  </si>
+  <si>
+    <t>forumJoinUserList</t>
+  </si>
+  <si>
+    <t>수강생 토론 성적 단순 목록 조회</t>
+  </si>
+  <si>
+    <t>selectProfMemo</t>
+  </si>
+  <si>
+    <t>교수자 메모 팝업용 정보 조회</t>
+  </si>
+  <si>
+    <t>editForumProfMemo</t>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
+  <si>
+    <t>교수자 메모(의견) 수정</t>
+  </si>
+  <si>
+    <t>getForumJoinUser</t>
+  </si>
+  <si>
+    <t>토론 참여자 테이블 존재 여부 카운트</t>
+  </si>
+  <si>
+    <t>getMemo</t>
+  </si>
+  <si>
+    <t>특정 학습자의 교수 메모만 조회</t>
+  </si>
+  <si>
+    <t>getSelectCtsLen</t>
+  </si>
+  <si>
+    <t>설정한 글자수 이상 작성한 참여자 수 체크</t>
+  </si>
+  <si>
+    <t>chkStdNoInsert</t>
+  </si>
+  <si>
+    <t>참여 데이터가 없을 경우 기본 데이터 삽입</t>
+  </si>
+  <si>
+    <t>insertJoinUser</t>
+  </si>
+  <si>
+    <t>모든 수강생을 토론 참여자로 일괄 삽입</t>
+  </si>
+  <si>
+    <t>participateScore</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">참여 여부에 따른 일괄 점수 부여 (MySQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>ON DUPLICATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 잔재 존재)</t>
+    </r>
+  </si>
+  <si>
+    <t>updateStdTeam</t>
+  </si>
+  <si>
+    <t>학습자의 소속 팀 정보 수정</t>
+  </si>
+  <si>
+    <t>updateJoinUserEvalN</t>
+  </si>
+  <si>
+    <t>평가 상태 초기화 (점수 삭제)</t>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>토론평가분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-ForumJoinUserMapper_SQL.xml]</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Query 필드 체크</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>루브릭점수' 토론에서는 제외됨.
+'시험대체' 등에서는 사용됨.
+---
+[3/18]
+1.AS-IS Code
+- R : 참여형
+- P : 점수형</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use Case</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.insertAtcl: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>토론</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>게시글</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">등록
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2.// EZ-Grader </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">메인
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    @RequestMapping(value = "/ezgMainForm.do")
+3. // </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">성적평가
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    @RequestMapping(value="/Form/scoreManage.do")
+4.// </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일괄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>피드백</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">팝업
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    @RequestMapping(value="/allForumFdbkPop.do")</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1651,7 +2032,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1719,8 +2100,38 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1751,6 +2162,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -1855,7 +2284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1952,6 +2381,35 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2210,7 +2668,7 @@
         <v>121</v>
       </c>
       <c r="H1" s="31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="38.25">
@@ -2275,7 +2733,7 @@
         <v>129</v>
       </c>
       <c r="H4" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="127.5">
@@ -2296,10 +2754,10 @@
         <v>20</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="51">
@@ -2322,10 +2780,10 @@
         <v>119</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:27" s="12" customFormat="1" ht="89.25">
@@ -2348,7 +2806,7 @@
         <v>120</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="H7" s="36"/>
       <c r="I7" s="11"/>
@@ -2467,7 +2925,7 @@
         <v>41</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="12.75">
@@ -2490,7 +2948,7 @@
         <v>41</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="12.75">
@@ -2513,7 +2971,7 @@
         <v>48</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="12.75">
@@ -2536,7 +2994,7 @@
         <v>48</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="12.75">
@@ -2559,7 +3017,7 @@
         <v>48</v>
       </c>
       <c r="H16" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="12.75">
@@ -2582,7 +3040,7 @@
         <v>48</v>
       </c>
       <c r="H17" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="51">
@@ -2606,7 +3064,7 @@
         <v>130</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="12.75">
@@ -2772,7 +3230,7 @@
         <v>48</v>
       </c>
       <c r="H26" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="12.75">
@@ -2852,7 +3310,7 @@
         <v>96</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="12.75">
@@ -2875,7 +3333,7 @@
         <v>96</v>
       </c>
       <c r="H31" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="12.75">
@@ -2993,12 +3451,12 @@
         <v>115</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1">
       <c r="A38" s="26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B38" s="26" t="s">
         <v>122</v>
@@ -3030,10 +3488,10 @@
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
       <c r="B40" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="H40" s="37" t="s">
         <v>138</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3041,4 +3499,242 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" style="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42" style="37" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" style="37" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.42578125" style="37" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="37" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.5">
+      <c r="A3" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="43"/>
+    </row>
+    <row r="4" spans="1:5" ht="25.5">
+      <c r="A4" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="43"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="43"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="43"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" s="43"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="43"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="43"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="43"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="43"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" s="43"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" s="43"/>
+    </row>
+    <row r="15" spans="1:5" ht="89.25">
+      <c r="A15" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="48" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="25.5">
+      <c r="A16" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="D16" s="43"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="43"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="43"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc2/TB_LMS_FORUM-TB_LMS_DSCS.xlsx
+++ b/doc2/TB_LMS_FORUM-TB_LMS_DSCS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="187">
   <si>
     <t>asis_column (기존)</t>
   </si>
@@ -1649,16 +1649,10 @@
     <t>설명</t>
   </si>
   <si>
-    <t>selectForumScoreStatus</t>
-  </si>
-  <si>
     <t>Select</t>
   </si>
   <si>
     <t>토론 현황(미참여, 완료, 평균/최고/최저 점수) 통계 조회</t>
-  </si>
-  <si>
-    <t>listPaging</t>
   </si>
   <si>
     <t>토론 참여 학습자 목록 조회 (페이징, 팀 정보, 참여 건수 포함)</t>
@@ -1700,9 +1694,6 @@
     <t>학습자별 참여 여부 및 팀 정보 목록 조회</t>
   </si>
   <si>
-    <t>selectForumJoinUser</t>
-  </si>
-  <si>
     <t>특정 학습자의 토론 참여 상세 정보 조회</t>
   </si>
   <si>
@@ -1745,19 +1736,10 @@
     <t>설정한 글자수 이상 작성한 참여자 수 체크</t>
   </si>
   <si>
-    <t>chkStdNoInsert</t>
-  </si>
-  <si>
     <t>참여 데이터가 없을 경우 기본 데이터 삽입</t>
   </si>
   <si>
-    <t>insertJoinUser</t>
-  </si>
-  <si>
     <t>모든 수강생을 토론 참여자로 일괄 삽입</t>
-  </si>
-  <si>
-    <t>participateScore</t>
   </si>
   <si>
     <r>
@@ -1845,6 +1827,69 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>selectForumJoinUser</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>selectForumScoreStatus</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>listPaging</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>chkStdNoInsert</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>insertJoinUser</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">forumMutInsert()
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>상호평가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>안씀</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른쪽 3번 토론평가 진입시 먼저 처리함.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">1.insertAtcl: </t>
     </r>
@@ -1933,22 +1978,35 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">    @RequestMapping(value = "/ezgMainForm.do")
-3. // </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">성적평가
 </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">3. // </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">토론평가
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
@@ -1956,6 +2014,63 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">    @RequestMapping(value="/Form/scoreManage.do")
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참여형일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>때만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 4.// </t>
     </r>
     <r>
@@ -2021,6 +2136,102 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">    @RequestMapping(value="/allForumFdbkPop.do")</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>participateScore</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1. // </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">토론평가
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    @RequestMapping(value="/Form/scoreManage.do")</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2.// </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참여형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">일괄평가
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    @RequestMapping(value="/participateScore.do")</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2032,7 +2243,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2130,8 +2341,25 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2180,8 +2408,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -2280,11 +2520,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2381,34 +2630,50 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2806,7 +3071,7 @@
         <v>120</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H7" s="36"/>
       <c r="I7" s="11"/>
@@ -3515,225 +3780,255 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="52" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.5">
+      <c r="A3" s="41" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="B2" s="41" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="44" t="s">
+      <c r="B3" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="43"/>
+      <c r="E3" s="38"/>
+    </row>
+    <row r="4" spans="1:5" ht="25.5">
+      <c r="A4" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="E2" s="44" t="s">
+      <c r="B4" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="43"/>
+      <c r="E4" s="38"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="43"/>
+      <c r="E5" s="38"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="38"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="E7" s="38"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="43"/>
+      <c r="E8" s="38"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="43"/>
+      <c r="E9" s="38"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="38"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" s="38"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="38"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="38"/>
+    </row>
+    <row r="14" spans="1:5" ht="25.5">
+      <c r="A14" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="D14" s="43" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="25.5">
-      <c r="A3" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="43"/>
-    </row>
-    <row r="4" spans="1:5" ht="25.5">
-      <c r="A4" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="40" t="s">
+      <c r="E14" s="38"/>
+    </row>
+    <row r="15" spans="1:5" ht="102">
+      <c r="A15" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="43"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="43"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="43"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="D7" s="43"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="43"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="38" t="s">
+      <c r="C15" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="51">
+      <c r="A16" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="38" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="B9" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="D9" s="43"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="D10" s="43"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="46" t="s">
-        <v>162</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="D12" s="43"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="D13" s="43"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="40" t="s">
+      <c r="C17" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="D14" s="43"/>
-    </row>
-    <row r="15" spans="1:5" ht="89.25">
-      <c r="A15" s="38" t="s">
+      <c r="D17" s="43"/>
+      <c r="E17" s="38"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="B15" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" s="40" t="s">
+      <c r="B18" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="48" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="25.5">
-      <c r="A16" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="D16" s="43"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="D17" s="43"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>177</v>
-      </c>
       <c r="D18" s="43"/>
+      <c r="E18" s="38"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
